--- a/member_deposit/会员沉淀分析_20260810.xlsx
+++ b/member_deposit/会员沉淀分析_20260810.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,14 +452,14 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22650</v>
+        <v>22667</v>
       </c>
       <c r="C2" t="n">
-        <v>22612</v>
+        <v>22629</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>+297</t>
+          <t>+314</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -473,14 +473,14 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>22482</v>
+        <v>22503</v>
       </c>
       <c r="C3" t="n">
-        <v>22481</v>
+        <v>22502</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>+932</t>
+          <t>+953</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -494,14 +494,14 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>48068</v>
+        <v>48097</v>
       </c>
       <c r="C4" t="n">
-        <v>48065</v>
+        <v>48094</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>+1081</t>
+          <t>+1110</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -515,14 +515,14 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>67678</v>
+        <v>67695</v>
       </c>
       <c r="C5" t="n">
-        <v>67642</v>
+        <v>67659</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>+1299</t>
+          <t>+1316</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -536,14 +536,14 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7973</v>
+        <v>7986</v>
       </c>
       <c r="C6" t="n">
-        <v>7973</v>
+        <v>7986</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>+384</t>
+          <t>+397</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -557,14 +557,14 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16093</v>
+        <v>16099</v>
       </c>
       <c r="C7" t="n">
-        <v>16093</v>
+        <v>16099</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>+259</t>
+          <t>+265</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -574,70 +574,51 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>（未匹配门店）</t>
+          <t>未消费会员</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14</v>
+        <v>12721</v>
       </c>
       <c r="C8" t="n">
-        <v>14</v>
+        <v>12583</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>+14</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
+          <t>+137</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>12584</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>未消费会员</t>
+          <t>合计</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12707</v>
+        <v>197768</v>
       </c>
       <c r="C9" t="n">
-        <v>12568</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>+123</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>12584</v>
-      </c>
+        <v>197552</v>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>合计</t>
+          <t>剔除-门店标记剔除（不计入）</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>197665</v>
-      </c>
-      <c r="C10" t="n">
-        <v>197448</v>
-      </c>
+        <v>13279</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>剔除-门店标记剔除（不计入）</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>13279</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -650,7 +631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:B1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -663,16 +644,6 @@
         <is>
           <t>记录数</t>
         </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>DJI上海LCM置汇旭辉广场授权体验店</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -737,11 +708,11 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DJI上海天荟广场授权体验店</t>
+          <t>DJI上海LCM置汇旭辉广场授权体验店</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>139</v>
+        <v>14</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
@@ -755,11 +726,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DJI上海陆家嘴中心L+mall授权体验店</t>
+          <t>DJI上海天荟广场授权体验店</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>409</v>
+        <v>140</v>
       </c>
       <c r="D4" t="n">
         <v>3</v>
@@ -773,11 +744,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DJI上海百联南桥购物中心授权体验店</t>
+          <t>DJI上海陆家嘴中心L+mall授权体验店</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>444</v>
+        <v>409</v>
       </c>
       <c r="D5" t="n">
         <v>4</v>
@@ -791,11 +762,11 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DJI上海第一八佰伴授权体验店</t>
+          <t>DJI上海百联南桥购物中心授权体验店</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>473</v>
+        <v>444</v>
       </c>
       <c r="D6" t="n">
         <v>5</v>
@@ -849,7 +820,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D9" t="n">
         <v>3</v>
@@ -921,7 +892,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D13" t="n">
         <v>2</v>
@@ -1065,7 +1036,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -1083,7 +1054,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D22" t="n">
         <v>1</v>
@@ -1119,7 +1090,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D24" t="n">
         <v>3</v>
@@ -1173,7 +1144,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D27" t="n">
         <v>1</v>
